--- a/output/2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -485,7 +485,6 @@
           <t>02 537 13 13 / 051 358 799</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Verificato: rivenditore utensili elettrici e manuali per falegnami e hobbisti (Makita, Bosch, Ferm, Dewalt), sede Obrtna ulica 24, Murska Sobota. Fonti: itis.siol.net, moja-dejavnost.si, abprodukt.si/o-nas. Email non reperita (non confondere con altra societa' omonima AB PRODUKT d.o.o. di Koper, entita' diversa).</t>
@@ -518,11 +517,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Verificato: seconda sede/filiale della stessa ditta di Murska Sobota, confermata come una delle due sedi in Pomurje (fonti: poisci.me, topponudba.com). Indirizzo e contatti specifici non riscontrati in fonti indipendenti - lasciati vuoti.</t>
+          <t>Verificato: seconda sede/filiale della stessa ditta di Murska Sobota, confermata come una delle due sedi in Pomurje (fonti: poisci.me, topponudba.com). Indirizzo e contatti specifici non riscontrati in fonti indipendenti - lasciati vuoti. [DUPLICATO — vedi anche: 2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -537,7 +534,6 @@
           <t>CDC, družba za trgovino, montažo in svetovanje d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Murska Sobota</t>
@@ -602,7 +598,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Verificato: catena nazionale ferramenta/utensili/materiali edili, sede Markišavska ulica 30, Murska Sobota. Fonti: merkur.si, najdi.si, cybo.com. Rivenditore generalista, non esclusivo di utensili/macchine utensili.</t>
+          <t>Verificato: catena nazionale ferramenta/utensili/materiali edili, sede Markišavska ulica 30, Murska Sobota. Fonti: merkur.si, najdi.si, cybo.com. Rivenditore generalista, non esclusivo di utensili/macchine utensili. [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -763,7 +759,6 @@
           <t>02 530 8840</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Verificato: sede Markišavska ulica 9, Murska Sobota. Vende materiali per falegnameria/edilizia, utensili e attrezzi da taglio e commercializza/assiste macchine per lavorazione legno e metallo (fonte: dimpex.si). Email specifica filiale non reperita.</t>
@@ -894,7 +889,6 @@
           <t>02 534 87 00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>fuori target settore: distributore di pneumatici/cerchi/ricambi auto e servizi officina veicoli, non utensileria/macchine utensili</t>

--- a/output/2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
